--- a/Margyn_Data_Template.xlsx
+++ b/Margyn_Data_Template.xlsx
@@ -25,9 +25,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="57">
-  <si>
-    <t xml:space="preserve">margyn</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="45">
+  <si>
+    <t xml:space="preserve">        margyn</t>
   </si>
   <si>
     <t xml:space="preserve">SME DATA TEMPLATE</t>
@@ -36,34 +36,119 @@
     <t xml:space="preserve">How to use this file</t>
   </si>
   <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fill in each of the five sheets below with your figures — one row per account, invoice, or bill.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Don't rename the sheets or the column headers. Margyn matches your data by name when you upload.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The amber row on each sheet is an example — delete it before you upload, or just overwrite it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leave a cell as 0 or blank if it doesn't apply to you.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Save the file, then go to Upload &amp; calculate → Upload workbook in the app and drop it in.</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF12805A"/>
+        <rFont val="Consolas"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">01   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0B1220"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Fill in each of the five sheets below with your figures — one row per account, invoice, or bill.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF12805A"/>
+        <rFont val="Consolas"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">02   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0B1220"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Don't rename the sheets or the column headers. Margyn matches your data by name when you upload.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF12805A"/>
+        <rFont val="Consolas"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">03   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0B1220"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Every sheet is blank below the header — no example data to delete, just start typing.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF12805A"/>
+        <rFont val="Consolas"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">04   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0B1220"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Leave a cell as 0 or blank if it doesn't apply to you.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF12805A"/>
+        <rFont val="Consolas"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">05   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0B1220"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Save the file, then go to Upload &amp; calculate → Upload workbook in the app and drop it in.</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">What's on each sheet</t>
@@ -99,6 +184,9 @@
     <t xml:space="preserve">Your monthly GST payable alongside available and claimed input tax credit.</t>
   </si>
   <si>
+    <t xml:space="preserve">       margyn</t>
+  </si>
+  <si>
     <t xml:space="preserve">BANK ACCOUNTS</t>
   </si>
   <si>
@@ -108,10 +196,7 @@
     <t xml:space="preserve">Balance</t>
   </si>
   <si>
-    <t xml:space="preserve">HDFC Current A/c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amber row is an example — replace with your accounts, one per row.</t>
+    <t xml:space="preserve">Add one row per bank account below — no example data, just start typing.</t>
   </si>
   <si>
     <t xml:space="preserve">RECEIVABLES</t>
@@ -132,16 +217,7 @@
     <t xml:space="preserve">Amount Received</t>
   </si>
   <si>
-    <t xml:space="preserve">Acme Textiles Pvt Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amber row is an example. Amount minus Amount Received becomes the open invoice.</t>
+    <t xml:space="preserve">Add one row per open invoice below. Amount minus Amount Received becomes the open balance.</t>
   </si>
   <si>
     <t xml:space="preserve">PAYABLES</t>
@@ -150,16 +226,7 @@
     <t xml:space="preserve">Vendor</t>
   </si>
   <si>
-    <t xml:space="preserve">Raw Materials Supplier Co</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amber row is an example — one row per open bill.</t>
+    <t xml:space="preserve">Add one row per open bill below — no example data, just start typing.</t>
   </si>
   <si>
     <t xml:space="preserve">P&amp;L SUMMARY</t>
@@ -192,10 +259,7 @@
     <t xml:space="preserve">ITC Claimed</t>
   </si>
   <si>
-    <t xml:space="preserve">June 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amber row is an example. ITC Available minus ITC Claimed is your unclaimed leakage.</t>
+    <t xml:space="preserve">Add one row per month below. ITC Available minus ITC Claimed is your unclaimed leakage.</t>
   </si>
 </sst>
 </file>
@@ -206,7 +270,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -231,7 +295,7 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="28"/>
+      <sz val="24"/>
       <color rgb="FF12805A"/>
       <name val="Georgia"/>
       <family val="0"/>
@@ -284,7 +348,7 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="22"/>
+      <sz val="20"/>
       <color rgb="FF12805A"/>
       <name val="Georgia"/>
       <family val="0"/>
@@ -308,14 +372,6 @@
     </font>
     <font>
       <i val="true"/>
-      <sz val="10.5"/>
-      <color rgb="FF5C6B7A"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
       <sz val="9"/>
       <color rgb="FF5C6B7A"/>
       <name val="Calibri"/>
@@ -330,7 +386,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -347,12 +403,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF0B1220"/>
         <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE7C7"/>
-        <bgColor rgb="FFD8DBE0"/>
       </patternFill>
     </fill>
     <fill>
@@ -411,13 +461,13 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -432,24 +482,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -460,27 +506,15 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -513,7 +547,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFBE7C7"/>
+      <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -554,6 +588,258 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>247320</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>247320</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="106200" y="133200"/>
+          <a:ext cx="247320" cy="247320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>190080</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>190080</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="106200" y="133200"/>
+          <a:ext cx="190080" cy="190080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>190080</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>190080</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="106200" y="133200"/>
+          <a:ext cx="190080" cy="190080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>190080</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>190080</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="106200" y="133200"/>
+          <a:ext cx="190080" cy="190080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>190080</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>190080</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="106200" y="133200"/>
+          <a:ext cx="190080" cy="190080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>190080</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>190080</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="106200" y="133200"/>
+          <a:ext cx="190080" cy="190080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -736,127 +1022,125 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="B1:C21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="1.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="70"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="4"/>
-    </row>
-    <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="C6" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C8" s="5"/>
+    </row>
+    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="C9" s="5"/>
+    </row>
+    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C10" s="5"/>
+    </row>
+    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="C11" s="5"/>
+    </row>
+    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="C12" s="5"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="C15" s="4"/>
+    </row>
+    <row r="17" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="C17" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+    <row r="18" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="C18" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+    <row r="19" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="4"/>
-    </row>
-    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+      <c r="C19" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="8" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
+      <c r="C20" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="8" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
+      <c r="C21" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>23</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A12:B12"/>
+  <mergeCells count="9">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B15:C15"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -865,6 +1149,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -873,53 +1158,47 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="B1:C7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="1.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9"/>
-    </row>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="10"/>
-    </row>
-    <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="14"/>
+    <row r="1" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="8"/>
+    </row>
+    <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -928,6 +1207,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -936,82 +1216,67 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="B1:F7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="1.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-    </row>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
+    <row r="1" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-    </row>
-    <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>250000</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B7:F7"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1020,6 +1285,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1028,72 +1294,60 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="B1:E7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="1.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-    </row>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-    </row>
-    <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="11" t="s">
+    <row r="1" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+    </row>
+    <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="C5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="11" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>180000</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B7:E7"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1102,6 +1356,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1110,69 +1365,71 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="B1:C10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="1.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
+    <row r="1" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="8"/>
+    </row>
+    <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-    </row>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="10"/>
-    </row>
-    <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="17" t="n">
+    </row>
+    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="13" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="17" t="n">
+    <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="13" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B9" s="14"/>
+    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B10:C10"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1181,6 +1438,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1189,70 +1447,58 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="B1:E7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="1.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-    </row>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-    </row>
-    <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" s="13" t="n">
-        <v>240000</v>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>90000</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>65000</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
+    <row r="1" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+    </row>
+    <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B7:E7"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1261,5 +1507,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>